--- a/assets/data/marktplaats_volkswagen_emotional_seller_descriptions.xlsx
+++ b/assets/data/marktplaats_volkswagen_emotional_seller_descriptions.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volkswagen listings" sheetId="1" r:id="R2e666cd6ad3f4d89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" r:id="R5e4ae07554a44453"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volkswagen listings" sheetId="1" r:id="R6cbdaa78231b41e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" r:id="R9341cbf61aa34540"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -360,7 +360,7 @@
         <x:v>Price</x:v>
       </x:c>
       <x:c r="C1" s="5" t="str">
-        <x:v>Image links</x:v>
+        <x:v>Image links removed</x:v>
       </x:c>
       <x:c r="D1" s="5" t="str">
         <x:v>Additional info</x:v>
@@ -372,7 +372,7 @@
         <x:v>Description source</x:v>
       </x:c>
       <x:c r="G1" s="5" t="str">
-        <x:v>Listing URL</x:v>
+        <x:v>Listing URL removed</x:v>
       </x:c>
       <x:c r="H1" s="22" t="str">
         <x:v>Seller tone</x:v>
@@ -391,9 +391,7 @@
       <x:c r="B2" s="12" t="str">
         <x:v>€ 21.900,-</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/0b/0b206c7d-0405-420d-bc68-21e2b687e2b0?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C2" s="12" t="str"/>
       <x:c r="D2" s="12" t="str">
         <x:v>2021 · 132.030 km · Diesel · Handgeschakeld</x:v>
       </x:c>
@@ -401,11 +399,9 @@
         <x:v>A 2021 Volkswagen Transporter L2H1 with a 2.0 TDI diesel engine and manual gearbox. The van is presented as dealer maintained and well suited for everyday work use. It comes with air conditioning, navigation, Apple CarPlay, cruise control, a tow bar, parking sensors and Bluetooth. The seller also advertises a lease option from €356 per month.</x:v>
       </x:c>
       <x:c r="F2" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G2" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/a1529267603-volkswagen-transporter-l2-h1-lease-vanaf-356-p-mnd</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G2" s="12" t="str"/>
       <x:c r="H2" s="12" t="str">
         <x:v>Upbeat / ready to sell</x:v>
       </x:c>
@@ -423,9 +419,7 @@
       <x:c r="B3" s="12" t="str">
         <x:v>€ 13.950,-</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/ab35b171-c3c2-4586-90b1-45467d6cc99c?rule=ecg_mp_eps$_85</x:v>
-      </x:c>
+      <x:c r="C3" s="12" t="str"/>
       <x:c r="D3" s="12" t="str">
         <x:v>2021 · Benzine · Automaat · Hatchback | Adaptive Cruise Control, Cruise Control, Climate control, + 31 opties</x:v>
       </x:c>
@@ -433,11 +427,9 @@
         <x:v>A well-equipped 2021 Volkswagen Polo Comfortline with a 95 hp petrol engine and 7-speed automatic transmission. It features a digital cockpit, adaptive cruise control, navigation, automatic climate control, wireless phone charging, DAB radio, parking sensors and LED lighting. Driver-assistance equipment includes collision warning and other safety systems.</x:v>
       </x:c>
       <x:c r="F3" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435929856-volkswagen-polo-1-0-tsi-comfortline-automaat-climate-contro</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="str"/>
       <x:c r="H3" s="12" t="str">
         <x:v>Proud / confident</x:v>
       </x:c>
@@ -455,9 +447,7 @@
       <x:c r="B4" s="12" t="str">
         <x:v>€ 23.950,-</x:v>
       </x:c>
-      <x:c r="C4" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/c8f39790-c6f0-4eaf-8cd2-3de49a37dbb6?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/838706ef-004c-404c-a340-3beb0c7877c9?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/18096af1-a8d5-4275-9840-bd42aa68b368?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C4" s="12" t="str"/>
       <x:c r="D4" s="12" t="str">
         <x:v>2022 · 68.730 km · Benzine · Automaat · Hatchback | Parkeerassistent, Adaptive Cruise Control, Cruise Control, + 42 opties | APK bij aflevering | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -467,9 +457,7 @@
       <x:c r="F4" s="12" t="str">
         <x:v>Listing card only</x:v>
       </x:c>
-      <x:c r="G4" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435920247-volkswagen-polo-1-0-tsi-2x-r-line-panoramadak-beats-by-d</x:v>
-      </x:c>
+      <x:c r="G4" s="12" t="str"/>
       <x:c r="H4" s="12" t="str">
         <x:v>Excited / sporty</x:v>
       </x:c>
@@ -487,9 +475,7 @@
       <x:c r="B5" s="12" t="str">
         <x:v>€ 14.995,-</x:v>
       </x:c>
-      <x:c r="C5" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/ed4c70a0-4e19-49e9-9f40-362ddfaabbca?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/c51a08d7-4128-4c81-90ce-271bf8045f6a?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/11060702-e484-49a8-bcf6-471278aebe61?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C5" s="12" t="str"/>
       <x:c r="D5" s="12" t="str">
         <x:v>2007 · 152.000 km · Benzine · Automaat · Overige carrosserieën | 4x4 | Financiering mogelijk | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -499,9 +485,7 @@
       <x:c r="F5" s="12" t="str">
         <x:v>Exact listing/search snippet</x:v>
       </x:c>
-      <x:c r="G5" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435905423-dikke-golf-r32-dsg-pano-leer-5drs</x:v>
-      </x:c>
+      <x:c r="G5" s="12" t="str"/>
       <x:c r="H5" s="12" t="str">
         <x:v>Nostalgic enthusiast</x:v>
       </x:c>
@@ -519,9 +503,7 @@
       <x:c r="B6" s="12" t="str">
         <x:v>€ 1.600,-</x:v>
       </x:c>
-      <x:c r="C6" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/ee8210ce-bb2d-48b0-a517-5bfc0ebf7d24?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/89034f41-09e2-428b-bdef-318ca9f9b8ac?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/8faa289d-2654-4d45-bb2a-5e2e80020b30?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C6" s="12" t="str"/>
       <x:c r="D6" s="12" t="str">
         <x:v>2009 · 350.105 km · Benzine · Handgeschakeld · Stationwagon</x:v>
       </x:c>
@@ -529,11 +511,9 @@
         <x:v>A 2009 Volkswagen Passat Variant that the seller describes as a reliable daily car. The timing chain has recently been replaced, and the seller reports fuel consumption of roughly 1 litre per 15 km. Equipment includes air conditioning, cruise control, parking sensors and four electric windows. The seller also mentions that the rear brake pads can occasionally squeak, although they still function normally.</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G6" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2430477751-volkswagen-passat-1-4-tsi-90kw-variant-2009-grijs</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str"/>
       <x:c r="H6" s="12" t="str">
         <x:v>Honest / pragmatic</x:v>
       </x:c>
@@ -551,9 +531,7 @@
       <x:c r="B7" s="12" t="str">
         <x:v>€ 16.499,-</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/575f5040-1d8a-49bf-84b3-c07d486b05e1?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/7f37b5a5-da31-4012-b1b5-4f686ea388e3?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/fbb97d26-6e2d-43c4-8c97-f86901bc4d77?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C7" s="12" t="str"/>
       <x:c r="D7" s="12" t="str">
         <x:v>2021 · 146.359 km · Benzine · Handgeschakeld · SUV of Terreinwagen | Adaptive Cruise Control, Cruise Control, Parkeersensor, + 27 opties | NAP gecontroleerd | Financiering mogelijk | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -561,11 +539,9 @@
         <x:v>A 2021 Volkswagen T-Roc Style described as a tidy and well-maintained car. It has two keys and is said to have been dealer maintained. Equipment includes a digital cockpit, adaptive cruise control, navigation, DAB radio, parking sensors, air conditioning and lane/collision-assistance features. Financing, insurance and an optional delivery package are available.</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G7" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2431722765-volkswagen-t-roc-1-0-tsi-style-5deurs-airco-elek-pakket</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="str"/>
       <x:c r="H7" s="12" t="str">
         <x:v>Friendly / upbeat</x:v>
       </x:c>
@@ -583,9 +559,7 @@
       <x:c r="B8" s="12" t="str">
         <x:v>€ 17.899,-</x:v>
       </x:c>
-      <x:c r="C8" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/7518b4f9-3e9a-4f9a-b312-c53a3027da64?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/fa7f0a52-ecd6-4e24-ad23-d737f63138a1?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/cef2877e-ec10-45a6-ad6c-57d8fa44b249?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C8" s="12" t="str"/>
       <x:c r="D8" s="12" t="str">
         <x:v>2018 · 176.231 km · Benzine · Automaat · Stationwagon | Parkeerassistent, Adaptive Cruise Control, Trekhaak, + 37 opties | NAP gecontroleerd | Financiering mogelijk | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -593,11 +567,9 @@
         <x:v>A well-maintained 2018 Volkswagen Passat Variant Highline Business R-Line, advertised as damage-free. It is equipped with a panoramic roof, electric tailgate, leather upholstery, heated sport seats, 18-inch alloy wheels, LED headlights, a tow bar with trailer assist, digital cockpit, adaptive cruise control, navigation and automatic climate control.</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2430852586-volkswagen-passat-variant-1-4-tsi-highline-business-r-line</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str"/>
       <x:c r="H8" s="12" t="str">
         <x:v>Proud / premium</x:v>
       </x:c>
@@ -615,9 +587,7 @@
       <x:c r="B9" s="12" t="str">
         <x:v>€ 20.950,-</x:v>
       </x:c>
-      <x:c r="C9" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/3eb0fec8-0ec3-49b6-a999-d792324f499a?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/456791a5-1dd8-4f41-a68e-2249593a9431?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/90ef4df1-fa64-4c3d-b7f9-f59f3bfd4557?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C9" s="12" t="str"/>
       <x:c r="D9" s="12" t="str">
         <x:v>2018 · 169.597 km · Benzine · Automaat · SUV of Terreinwagen | Adaptive Cruise Control, Trekhaak, Cruise Control, + 36 opties | NAP gecontroleerd | Financiering mogelijk | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -625,11 +595,9 @@
         <x:v>A 2018 Volkswagen Tiguan Highline Business R-Line that is described as well maintained and damage-free. The car comes with two keys and features R-Line styling, sport seats, an electric tailgate, LED headlights, digital cockpit, adaptive cruise control, navigation, wireless phone charging, lane/collision assistance and a tow bar.</x:v>
       </x:c>
       <x:c r="F9" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2434773101-volkswagen-tiguan-1-4-tsi-act-highline-business-r-line-autom</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G9" s="12" t="str"/>
       <x:c r="H9" s="12" t="str">
         <x:v>Reluctant / slightly sad</x:v>
       </x:c>
@@ -647,9 +615,7 @@
       <x:c r="B10" s="12" t="str">
         <x:v>€ 17.950,-</x:v>
       </x:c>
-      <x:c r="C10" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/bac8e2fa-313f-40db-9943-86196ca2a7f7?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/4f047c94-b351-4286-a867-9bacdb527c1e?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/e6654b92-df41-4086-bee5-eede9336e4bc?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C10" s="12" t="str"/>
       <x:c r="D10" s="12" t="str">
         <x:v>2021 · 110.982 km · Benzine · Automaat · Hatchback | Adaptive Cruise Control, Trekhaak, Cruise Control, + 23 opties | NAP gecontroleerd | Financiering mogelijk | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -657,11 +623,9 @@
         <x:v>A blue 2021 Volkswagen Polo R-Line Edition with an automatic transmission. The seller describes it as very well maintained and damage-free, with dealer service history and two keys. Equipment includes a tow bar, adaptive cruise control, DAB radio and parking sensors. Financing and warranty options are available.</x:v>
       </x:c>
       <x:c r="F10" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G10" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2433162803-volkswagen-polo-1-0-tsi-r-line-edition-automaat-110-000k</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="str"/>
       <x:c r="H10" s="12" t="str">
         <x:v>Motivated seller</x:v>
       </x:c>
@@ -679,9 +643,7 @@
       <x:c r="B11" s="12" t="str">
         <x:v>€ 13.950,-</x:v>
       </x:c>
-      <x:c r="C11" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/c7d86fb6-6455-41ed-bbd5-11aed54e0505?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/3c7d2965-f9e6-464b-b0d2-aa65e45556a5?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/bcce92b9-056f-4374-8ed6-faa1a9245ad2?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C11" s="12" t="str"/>
       <x:c r="D11" s="12" t="str">
         <x:v>2021 · 168.198 km · Benzine · Handgeschakeld · Hatchback | Adaptive Cruise Control, Cruise Control, Climate control, + 29 opties | NAP gecontroleerd | Financiering mogelijk | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -691,9 +653,7 @@
       <x:c r="F11" s="12" t="str">
         <x:v>Exact listing/search snippet</x:v>
       </x:c>
-      <x:c r="G11" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2433157068-volkswagen-polo-1-0-tsi-highline-business-r-line-handbak</x:v>
-      </x:c>
+      <x:c r="G11" s="12" t="str"/>
       <x:c r="H11" s="12" t="str">
         <x:v>No-nonsense</x:v>
       </x:c>
@@ -711,9 +671,7 @@
       <x:c r="B12" s="12" t="str">
         <x:v>€ 21.950,-</x:v>
       </x:c>
-      <x:c r="C12" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/da0b6c60-9f2f-4902-aee7-3847f57a617a?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/ad6a05e9-ce23-46f4-a3bc-f45bbf247b0c?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/fead8b1b-d3a1-48e6-a31c-51ca424b91a3?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C12" s="12" t="str"/>
       <x:c r="D12" s="12" t="str">
         <x:v>2022 · 144.675 km · Hybride Elektrisch/Benzine · Automaat · Stationwagon | Parkeercamera, Climate control, Parkeersensor, + 33 opties | NAP gecontroleerd | Financiering mogelijk | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -723,9 +681,7 @@
       <x:c r="F12" s="12" t="str">
         <x:v>Listing card only</x:v>
       </x:c>
-      <x:c r="G12" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435657585-volkswagen-golf-variant-1-5-etsi-style-automaat-airco</x:v>
-      </x:c>
+      <x:c r="G12" s="12" t="str"/>
       <x:c r="H12" s="12" t="str">
         <x:v>Practical / family-minded</x:v>
       </x:c>
@@ -743,9 +699,7 @@
       <x:c r="B13" s="12" t="str">
         <x:v>€ 19.750,-</x:v>
       </x:c>
-      <x:c r="C13" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/8d02cffe-e016-4570-a970-025beb8e3593?rule=ecg_mp_eps$_85</x:v>
-      </x:c>
+      <x:c r="C13" s="12" t="str"/>
       <x:c r="D13" s="12" t="str">
         <x:v>2021 · 86.777 km · Benzine · Handgeschakeld · Hatchback | Parkeerassistent, Adaptive Cruise Control, Cruise Control, + 38 opties</x:v>
       </x:c>
@@ -753,11 +707,9 @@
         <x:v>A 2021 Volkswagen Golf 8 with a 1.5 TSI petrol engine, described by the private seller as a very nice and economical car. It is a German import and a Carscanner report is available. The APK is valid until October 2027. The car has newer 18-inch wheels and tyres, while the original 16-inch wheels with all-weather tyres are also included. Two keys are supplied, and the seller says the car is being sold because a larger vehicle was purchased.</x:v>
       </x:c>
       <x:c r="F13" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G13" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2427554353-volkswagen-golf-1-5-tsi-130pk-2021-zwart</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G13" s="12" t="str"/>
       <x:c r="H13" s="12" t="str">
         <x:v>Nostalgic / reluctant</x:v>
       </x:c>
@@ -775,9 +727,7 @@
       <x:c r="B14" s="12" t="str">
         <x:v>€ 14.950,-</x:v>
       </x:c>
-      <x:c r="C14" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/4c6890f1-c423-43ed-85e5-35217b55a5c9?rule=ecg_mp_eps$_85</x:v>
-      </x:c>
+      <x:c r="C14" s="12" t="str"/>
       <x:c r="D14" s="12" t="str">
         <x:v>2015 · Benzine · Automaat · Hatchback</x:v>
       </x:c>
@@ -787,9 +737,7 @@
       <x:c r="F14" s="12" t="str">
         <x:v>Exact listing/search snippet</x:v>
       </x:c>
-      <x:c r="G14" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435890324-volkswagen-golf-2-0-tsi-gti-performance-inruil-mogelijk</x:v>
-      </x:c>
+      <x:c r="G14" s="12" t="str"/>
       <x:c r="H14" s="12" t="str">
         <x:v>Enthusiast / protective</x:v>
       </x:c>
@@ -807,9 +755,7 @@
       <x:c r="B15" s="12" t="str">
         <x:v>€ 16.500,-</x:v>
       </x:c>
-      <x:c r="C15" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/746dfca1-5c9d-41a8-9fe3-ad78b4162ed4?rule=ecg_mp_eps$_85</x:v>
-      </x:c>
+      <x:c r="C15" s="12" t="str"/>
       <x:c r="D15" s="12" t="str">
         <x:v>2023 · 28.095 km · Benzine · Handgeschakeld · Hatchback</x:v>
       </x:c>
@@ -837,9 +783,7 @@
       <x:c r="B16" s="12" t="str">
         <x:v>€ 22.950,-</x:v>
       </x:c>
-      <x:c r="C16" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/463af418-cd72-49fb-9a8d-8808b05badf7?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/b5f31b05-ca9f-4717-bb11-2b61b89c3bce?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/b4c1c577-0a4a-45c6-994f-e69959692de7?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C16" s="12" t="str"/>
       <x:c r="D16" s="12" t="str">
         <x:v>2021 · 106.689 km · Hybride Elektrisch/Benzine · Automaat · Stationwagon | Parkeerassistent, Adaptive Cruise Control, Trekhaak, + 58 opties | Financiering mogelijk | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -847,11 +791,9 @@
         <x:v>A 2021 Volkswagen Passat Variant GTE plug-in hybrid with 218 hp. The car is highly equipped, including a panoramic roof, full leather interior, folding tow bar, reversing camera, Matrix LED headlights, electric tailgate, virtual cockpit, heated seats and keyless entry/start. It also has adaptive cruise control and lane-assistance systems. The seller states that it has been dealer maintained, had one owner and comes with two keys.</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G16" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2430840072-volkswagen-passat-variant-1-4-tsi-phev-gte-218pk-pano-volled</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G16" s="12" t="str"/>
       <x:c r="H16" s="12" t="str">
         <x:v>Proud / premium</x:v>
       </x:c>
@@ -869,9 +811,7 @@
       <x:c r="B17" s="12" t="str">
         <x:v>€ 19.850,-</x:v>
       </x:c>
-      <x:c r="C17" s="12" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/22/227b2186-69c4-4745-b0bd-41dc6531456f?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C17" s="12" t="str"/>
       <x:c r="D17" s="12" t="str">
         <x:v>2019 · 152.533 km · Diesel · Handgeschakeld</x:v>
       </x:c>
@@ -879,11 +819,9 @@
         <x:v>A 2019 Volkswagen Transporter L1H1 with a 2.0 TDI diesel engine producing 150 hp. The van is described as a strong, dealer-maintained vehicle that is also suitable for towing. Equipment includes navigation, air conditioning, Apple CarPlay and Android Auto, side bars, Bluetooth and other practical features. A lease example from €323 per month is advertised.</x:v>
       </x:c>
       <x:c r="F17" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G17" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/a1523517959-volkswagen-transporter-l1-h1-lease-vanaf-323-p-mnd</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G17" s="12" t="str"/>
       <x:c r="H17" s="12" t="str">
         <x:v>Businesslike / practical</x:v>
       </x:c>
@@ -901,9 +839,7 @@
       <x:c r="B18" s="12" t="str">
         <x:v>€ 18.950,-</x:v>
       </x:c>
-      <x:c r="C18" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/15f144f9-ad35-4656-a1c2-7e86f374ae50?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/066c3779-b52b-466b-aa42-b1915d008b35?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/bf884f55-e439-4917-a7bc-935691e16b6c?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C18" s="12" t="str"/>
       <x:c r="D18" s="12" t="str">
         <x:v>2023 · 121.322 km · Benzine · Automaat · Hatchback | Parkeerassistent, Adaptive Cruise Control, Cruise Control, + 51 opties | Financiering mogelijk | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -911,11 +847,9 @@
         <x:v>A 2023 Volkswagen Polo Style with the 110 hp petrol engine and DSG automatic gearbox, finished in Deep Black. It is said to be dealer maintained and comes with two keys. Equipment includes a panoramic roof, adaptive cruise control with Stop &amp; Go, navigation, wireless phone charging, heated seats, reversing camera, Matrix/IQ LED headlights, digital cockpit, lane assist, parking sensors and Apple CarPlay/Android Auto.</x:v>
       </x:c>
       <x:c r="F18" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G18" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2430447370-volkswagen-polo-1-0-tsi-style-dsg-110pk-facelift-pano-trek-c</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G18" s="12" t="str"/>
       <x:c r="H18" s="12" t="str">
         <x:v>Excited / enthusiastic</x:v>
       </x:c>
@@ -933,9 +867,7 @@
       <x:c r="B19" s="12" t="str">
         <x:v>€ 25.450,-</x:v>
       </x:c>
-      <x:c r="C19" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/9e2289f4-c047-4e67-8288-d2e6a789303a?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/edce2a19-8e68-45d1-a4ab-50d7ffa35ef0?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/9db2feba-9768-4417-9448-c5eec6e72ab8?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C19" s="12" t="str"/>
       <x:c r="D19" s="12" t="str">
         <x:v>2022 · 60.412 km · Benzine · Automaat · SUV of Terreinwagen | Adaptive Cruise Control, Trekhaak, Cruise Control, + 49 opties | Financiering mogelijk | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -945,9 +877,7 @@
       <x:c r="F19" s="12" t="str">
         <x:v>Exact listing/search snippet</x:v>
       </x:c>
-      <x:c r="G19" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2430548953-volkswagen-taigo-1-5-tsi-2x-r-line-black-style-pano-iq-led-v</x:v>
-      </x:c>
+      <x:c r="G19" s="12" t="str"/>
       <x:c r="H19" s="12" t="str">
         <x:v>Playful / stylish</x:v>
       </x:c>
@@ -965,9 +895,7 @@
       <x:c r="B20" s="12" t="str">
         <x:v>€ 22.950,-</x:v>
       </x:c>
-      <x:c r="C20" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/4f9ce412-5e40-4adf-80e0-88f50b7db82d?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/a61ac678-edf5-4e6d-98d4-17fca70a2a84?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/48d6ea58-d01a-4a96-99a1-94a2367f0630?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C20" s="12" t="str"/>
       <x:c r="D20" s="12" t="str">
         <x:v>2023 · 118.459 km · Benzine · Automaat · SUV of Terreinwagen | Adaptive Cruise Control, Cruise Control, Parkeercamera, + 52 opties | Financiering mogelijk | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -977,9 +905,7 @@
       <x:c r="F20" s="12" t="str">
         <x:v>Exact listing/search snippet</x:v>
       </x:c>
-      <x:c r="G20" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435732443-volkswagen-taigo-1-5-tsi-2x-r-line-150pk-pano-iq-led-kessy-c</x:v>
-      </x:c>
+      <x:c r="G20" s="12" t="str"/>
       <x:c r="H20" s="12" t="str">
         <x:v>Reluctant / careful owner</x:v>
       </x:c>
@@ -997,9 +923,7 @@
       <x:c r="B21" s="12" t="str">
         <x:v>€ 18.575,-</x:v>
       </x:c>
-      <x:c r="C21" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/ef11f99e-8822-4655-a149-9ab9016fec17?rule=ecg_mp_eps$_85</x:v>
-      </x:c>
+      <x:c r="C21" s="12" t="str"/>
       <x:c r="D21" s="12" t="str">
         <x:v>2019 · 143.415 km · Benzine · Automaat · SUV of Terreinwagen | Parkeerassistent, Adaptive Cruise Control, Trekhaak, + 39 opties</x:v>
       </x:c>
@@ -1007,11 +931,9 @@
         <x:v>A 2019 Volkswagen T-Roc Highline with DSG automatic transmission. The private seller describes it as very neat, well maintained, damage-free, smoke-free and pet-free, with documented maintenance and all keys included. Equipment includes adaptive cruise control, reversing camera, park assist, Apple CarPlay/Android Auto, navigation, heated seat and steering wheel, LED lighting, lane and blind-spot assistance and a tow bar. APK is valid until July 2028.</x:v>
       </x:c>
       <x:c r="F21" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G21" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2425733827-volkswagen-t-roc-1-5-tsi-150pk-7-dsg-2019-apk-tot-juli-2028</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="str"/>
       <x:c r="H21" s="12" t="str">
         <x:v>Trust-building / sincere</x:v>
       </x:c>
@@ -1029,9 +951,7 @@
       <x:c r="B22" s="12" t="str">
         <x:v>€ 3.250,-</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/0b723bef-90aa-44fd-9d4e-306e9cc266d8?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/bd7a6292-a2ac-42ba-981f-26dab40312c6?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/84d33c1e-c72b-4f5c-83ef-f933fdab291a?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C22" s="12" t="str"/>
       <x:c r="D22" s="12" t="str">
         <x:v>2004 · 158.846 km · Benzine · Handgeschakeld · Hatchback | Cruise Control, Climate control, Automatische klimaatregeling, + 10 opties | NAP gecontroleerd | APK bij aflevering | Financiering mogelijk | Onderhoudsboekje | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -1041,9 +961,7 @@
       <x:c r="F22" s="12" t="str">
         <x:v>Listing card only</x:v>
       </x:c>
-      <x:c r="G22" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435850811-volkswagen-golf-1-4-trendline-airco-stuurbekrachtiging-ca</x:v>
-      </x:c>
+      <x:c r="G22" s="12" t="str"/>
       <x:c r="H22" s="12" t="str">
         <x:v>Nostalgic / honest</x:v>
       </x:c>
@@ -1061,9 +979,7 @@
       <x:c r="B23" s="12" t="str">
         <x:v>€ 20.999,-</x:v>
       </x:c>
-      <x:c r="C23" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/3fbe956c-b3df-46aa-bc55-1bbf0bd1b86c?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/3c8587e7-62c6-4314-b5e1-b71cefa31fb8?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/995ed170-260c-46b8-b1aa-faaccaf9c688?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C23" s="12" t="str"/>
       <x:c r="D23" s="12" t="str">
         <x:v>2019 · 152.829 km · Benzine · Automaat · Hatchback | Parkeerassistent, Adaptive Cruise Control, Cruise Control, + 53 opties</x:v>
       </x:c>
@@ -1071,11 +987,9 @@
         <x:v>A 2019 Volkswagen Golf 7.5 GTI Performance that the private seller has owned for almost five years. According to the seller, it was originally bought from a Volkswagen dealer and has been fully dealer maintained. The car comes with its booklets and two keys. All four tyres were replaced around six months ago, and the oil and filter were changed in August. The seller also mentions GTI accessories and detailing products that can be included with the car.</x:v>
       </x:c>
       <x:c r="F23" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G23" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2432261293-golf-7-5-gti-performance-245pk-2019-pano-dealer-onderhouden</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G23" s="12" t="str"/>
       <x:c r="H23" s="12" t="str">
         <x:v>Enthusiast / sentimental</x:v>
       </x:c>
@@ -1093,9 +1007,7 @@
       <x:c r="B24" s="12" t="str">
         <x:v>€ 7.450,-</x:v>
       </x:c>
-      <x:c r="C24" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/010b1602-0f07-4e04-ae98-3207b78a2c84?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/7ef0b08e-b342-47af-8042-46d35da61c8b?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/3e0cf74c-5644-4dfb-a9c0-d7d27fef3d18?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C24" s="12" t="str"/>
       <x:c r="D24" s="12" t="str">
         <x:v>2017 · 60.775 km · Benzine · Handgeschakeld · Hatchback | Start-stop-systeem, Elektrische ramen, LED verlichting, + 18 opties | NAP gecontroleerd | APK bij aflevering | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -1105,9 +1017,7 @@
       <x:c r="F24" s="12" t="str">
         <x:v>Exact listing/search snippet</x:v>
       </x:c>
-      <x:c r="G24" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435819746-volkswagen-up-1-0-bmt-move-up-60-775-km-airco-dab-4-seizo</x:v>
-      </x:c>
+      <x:c r="G24" s="12" t="str"/>
       <x:c r="H24" s="12" t="str">
         <x:v>Cheerful / lighthearted</x:v>
       </x:c>
@@ -1125,9 +1035,7 @@
       <x:c r="B25" s="12" t="str">
         <x:v>€ 21.750,-</x:v>
       </x:c>
-      <x:c r="C25" s="12" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/0f/0ffc1c93-ee87-4848-9788-a1d9ffa626e6?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C25" s="12" t="str"/>
       <x:c r="D25" s="12" t="str">
         <x:v>2021 · 156.749 km · Diesel · Handgeschakeld</x:v>
       </x:c>
@@ -1135,11 +1043,9 @@
         <x:v>A 2021 Volkswagen Transporter L1H1 Euro 6 that the seller describes as a good-driving, dealer-maintained van. It includes air conditioning, alloy wheels, Apple CarPlay and Android Auto, cruise control, a tow bar, parking sensors and Bluetooth. A lease example from €353 per month is also advertised.</x:v>
       </x:c>
       <x:c r="F25" s="12" t="str">
-        <x:v>Detail page</x:v>
-      </x:c>
-      <x:c r="G25" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/a1524055878-volkswagen-transporter-l1-h1-lease-vanaf-353-p-mnd</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="str"/>
       <x:c r="H25" s="12" t="str">
         <x:v>Businesslike / straightforward</x:v>
       </x:c>
@@ -1157,21 +1063,17 @@
       <x:c r="B26" s="12" t="str">
         <x:v>€ 11.950,-</x:v>
       </x:c>
-      <x:c r="C26" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/836d0dd2-7c2b-4352-9c90-2e7a6ab5469e?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/64148f77-3450-4ec8-81f7-7a0f3472b7ff?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/d6964d91-5ba6-4328-9f60-0b2b3debb5ff?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C26" s="12" t="str"/>
       <x:c r="D26" s="12" t="str">
         <x:v>2015 · 199.942 km · Hybride Elektrisch/Benzine · Automaat · Hatchback | Parkeerassistent, Trekhaak, Cruise Control, + 46 opties | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
       <x:c r="E26" s="12" t="str">
-        <x:v>A 2015 Volkswagen Golf GTE plug-in hybrid with an automatic transmission and 199,942 km. It is equipped with a panoramic roof, reversing camera, tow bar, park assist and cruise control, together with many other options. The original detail page description was not available, so this retelling is based on the information shown in the listing card.</x:v>
+        <x:v>A 2015 Volkswagen Golf GTE plug-in hybrid with an automatic transmission and 199,942 km. It is equipped with a panoramic roof, reversing camera, tow bar, park assist and cruise control, together with many other options. The original Provided listing copy description was not available, so this retelling is based on the information shown in the listing card.</x:v>
       </x:c>
       <x:c r="F26" s="12" t="str">
         <x:v>Listing card only</x:v>
       </x:c>
-      <x:c r="G26" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435814643-volkswagen-golf-1-4-tsi-gte-panorama-parkeern-camera-l</x:v>
-      </x:c>
+      <x:c r="G26" s="12" t="str"/>
       <x:c r="H26" s="12" t="str">
         <x:v>Flexible / bargain-minded</x:v>
       </x:c>
@@ -1179,7 +1081,7 @@
         <x:v>Negotiable</x:v>
       </x:c>
       <x:c r="J26" s="12" t="str">
-        <x:v>This GTE offers a lot of car for the money, especially if you want the panoramic roof and hybrid drivetrain without paying newer-car prices. A 2015 Volkswagen Golf GTE plug-in hybrid with an automatic transmission and 199,942 km. It is equipped with a panoramic roof, reversing camera, tow bar, park assist and cruise control, together with many other options. The original detail page description was not available, so this retelling is based on the information shown in the listing card. There’s room to talk on price, so feel free to make a sensible proposal.</x:v>
+        <x:v>This GTE offers a lot of car for the money, especially if you want the panoramic roof and hybrid drivetrain without paying newer-car prices. A 2015 Volkswagen Golf GTE plug-in hybrid with an automatic transmission and 199,942 km. It is equipped with a panoramic roof, reversing camera, tow bar, park assist and cruise control, together with many other options. The original Provided listing copy description was not available, so this retelling is based on the information shown in the listing card. There’s room to talk on price, so feel free to make a sensible proposal.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="112" customHeight="1">
@@ -1189,9 +1091,7 @@
       <x:c r="B27" s="12" t="str">
         <x:v>€ 21.950,-</x:v>
       </x:c>
-      <x:c r="C27" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/438d8b0c-686d-45d4-81b7-b71a4846286c?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/3eb957a4-b62b-41d7-b908-79fef028d294?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/d6bac02a-abc8-43e5-9985-0ae8c94a7d66?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C27" s="12" t="str"/>
       <x:c r="D27" s="12" t="str">
         <x:v>2020 · 88.364 km · Overige brandstoffen · Automaat · Overige carrosserieën | Cruise Control, Parkeercamera, Climate control, + 26 opties | APK bij aflevering | Financiering mogelijk | Dealer onderhouden</x:v>
       </x:c>
@@ -1201,9 +1101,7 @@
       <x:c r="F27" s="12" t="str">
         <x:v>Exact listing/search snippet</x:v>
       </x:c>
-      <x:c r="G27" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435804717-volkswagen-polo-gti-camera-navi-carplay-cruise-virtual</x:v>
-      </x:c>
+      <x:c r="G27" s="12" t="str"/>
       <x:c r="H27" s="12" t="str">
         <x:v>Excited / performance-focused</x:v>
       </x:c>
@@ -1221,9 +1119,7 @@
       <x:c r="B28" s="12" t="str">
         <x:v>€ 13.250,-</x:v>
       </x:c>
-      <x:c r="C28" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/7a2dd1dd-4c61-4aff-8156-024788c2461d?rule=ecg_mp_eps$_85</x:v>
-      </x:c>
+      <x:c r="C28" s="12" t="str"/>
       <x:c r="D28" s="12" t="str">
         <x:v>2018 · 84.345 km · Benzine · Handgeschakeld · Hatchback | Cruise Control, Climate control, Parkeersensor, + 25 opties</x:v>
       </x:c>
@@ -1233,9 +1129,7 @@
       <x:c r="F28" s="12" t="str">
         <x:v>Exact listing/search snippet</x:v>
       </x:c>
-      <x:c r="G28" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2432906153-volkswagen-up-1-0-tsi-gti-2018-5-deurs-115pk-nette-auto</x:v>
-      </x:c>
+      <x:c r="G28" s="12" t="str"/>
       <x:c r="H28" s="12" t="str">
         <x:v>Nostalgic / fun</x:v>
       </x:c>
@@ -1253,9 +1147,7 @@
       <x:c r="B29" s="12" t="str">
         <x:v>€ 23.450,-</x:v>
       </x:c>
-      <x:c r="C29" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/0a1488a2-77b6-40c7-ade1-bf6566843d32?rule=ecg_mp_eps$_85</x:v>
-      </x:c>
+      <x:c r="C29" s="12" t="str"/>
       <x:c r="D29" s="12" t="str">
         <x:v>2019 · 80.916 km · Benzine · Automaat · SUV of Terreinwagen | Adaptive Cruise Control, Cruise Control, Climate control, + 44 opties</x:v>
       </x:c>
@@ -1265,9 +1157,7 @@
       <x:c r="F29" s="12" t="str">
         <x:v>Listing card only</x:v>
       </x:c>
-      <x:c r="G29" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435799691-volkswagen-t-roc-1-5-tsi-sport-r-line-pano-acc-apple-carpl</x:v>
-      </x:c>
+      <x:c r="G29" s="12" t="str"/>
       <x:c r="H29" s="12" t="str">
         <x:v>Friendly / change-of-plans</x:v>
       </x:c>
@@ -1285,9 +1175,7 @@
       <x:c r="B30" s="12" t="str">
         <x:v>€ 18.950,-</x:v>
       </x:c>
-      <x:c r="C30" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/f3d3db19-96fb-49a7-9164-98c4e9ec89f4?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/17f4c107-2285-4aa7-9f2c-7020f99059e4?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/09cd9da7-ad90-4398-b9e9-689374b2e089?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C30" s="12" t="str"/>
       <x:c r="D30" s="12" t="str">
         <x:v>2015 · 189.765 km · Benzine · Automaat · Hatchback | Adaptive Cruise Control, Cruise Control, Parkeercamera, + 47 opties | Dealer onderhouden | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -1297,9 +1185,7 @@
       <x:c r="F30" s="12" t="str">
         <x:v>Listing card only</x:v>
       </x:c>
-      <x:c r="G30" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2435799241-volkswagen-golf-2-0-tsi-r-4motion-virtual-cockpit-panora</x:v>
-      </x:c>
+      <x:c r="G30" s="12" t="str"/>
       <x:c r="H30" s="12" t="str">
         <x:v>Reluctant / performance enthusiast</x:v>
       </x:c>
@@ -1317,9 +1203,7 @@
       <x:c r="B31" s="12" t="str">
         <x:v>€ 14.445,-</x:v>
       </x:c>
-      <x:c r="C31" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/923235bb-4003-4948-9691-0ce58a93e147?rule=ecg_mp_eps$_85 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/adf05bda-9919-407e-abd8-8522f9abfc83?rule=ecg_mp_eps$_83 ; https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/10d40239-6f1c-4c08-b334-1b771947fb91?rule=ecg_mp_eps$_83</x:v>
-      </x:c>
+      <x:c r="C31" s="12" t="str"/>
       <x:c r="D31" s="12" t="str">
         <x:v>2022 · 133.504 km · Benzine · Handgeschakeld · Hatchback | Adaptive Cruise Control, Cruise Control, Climate control, + 37 opties | Garantie: BOVAG | NAP gecontroleerd | APK bij aflevering | Financiering mogelijk | Onderhoudsboekje | Alle milieu/emissie zones</x:v>
       </x:c>
@@ -1329,9 +1213,7 @@
       <x:c r="F31" s="12" t="str">
         <x:v>Exact listing/search snippet</x:v>
       </x:c>
-      <x:c r="G31" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/volkswagen/m2426047988-volkswagen-polo-1-0-tsi-life-sport-virtual-cockpit-1e-eige</x:v>
-      </x:c>
+      <x:c r="G31" s="12" t="str"/>
       <x:c r="H31" s="12" t="str">
         <x:v>Practical / friendly</x:v>
       </x:c>
@@ -1350,7 +1232,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ecf71cac13d4152"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71b0aa1c156449e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1381,10 +1263,10 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>Description source: Detail page</x:v>
+        <x:v>Description source: Provided listing copy</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>The Marktplaats listing detail page was successfully retrieved.</x:v>
+        <x:v>The the source marketplace listing Provided listing copy was successfully retrieved.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1392,7 +1274,7 @@
         <x:v>Description source: Exact listing/search snippet</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>The exact listing could be identified from Marktplaats search/index text, but the detail page was not consistently retrievable.</x:v>
+        <x:v>The exact listing could be identified from the source marketplace search/index text, but the Provided listing copy was not consistently retrievable.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
